--- a/data/trans_orig/P58-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P58-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2007</t>
+          <t>Población según su lugar de nacimiento en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26828</t>
+          <t>27112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>19228</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47804</t>
+          <t>46135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>30577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64102</t>
+          <t>63731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48339</t>
+          <t>48106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22134</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44944</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45160</t>
+          <t>47305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81680</t>
+          <t>84370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>627891</t>
+          <t>628356</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>662057</t>
+          <t>660952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>606644</t>
+          <t>606087</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>640447</t>
+          <t>641411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1249503</t>
+          <t>1246775</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1295441</t>
+          <t>1295852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37620</t>
+          <t>38683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73487</t>
+          <t>75180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42499</t>
+          <t>42060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77748</t>
+          <t>78233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87770</t>
+          <t>87901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138079</t>
+          <t>138131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51332</t>
+          <t>48955</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92525</t>
+          <t>90528</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34316</t>
+          <t>34640</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63366</t>
+          <t>63272</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91619</t>
+          <t>92860</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143977</t>
+          <t>147127</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>812951</t>
+          <t>811497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>862261</t>
+          <t>863799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>840832</t>
+          <t>838205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>884358</t>
+          <t>883894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1665621</t>
+          <t>1664697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1736608</t>
+          <t>1735395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48352</t>
+          <t>49460</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87692</t>
+          <t>86351</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46135</t>
+          <t>45997</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83751</t>
+          <t>82335</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104217</t>
+          <t>105141</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155841</t>
+          <t>155905</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49083</t>
+          <t>48635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>88112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42978</t>
+          <t>42975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72733</t>
+          <t>73016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99089</t>
+          <t>100714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149607</t>
+          <t>149930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>517491</t>
+          <t>521404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>568554</t>
+          <t>571543</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>539277</t>
+          <t>540794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>585817</t>
+          <t>583191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1074146</t>
+          <t>1076143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1144265</t>
+          <t>1141725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,81%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51700</t>
+          <t>50744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88738</t>
+          <t>89344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54373</t>
+          <t>52903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97545</t>
+          <t>95117</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115232</t>
+          <t>116122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169175</t>
+          <t>171235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83788</t>
+          <t>84945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130711</t>
+          <t>131371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92916</t>
+          <t>92561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134661</t>
+          <t>134214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189443</t>
+          <t>188822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253918</t>
+          <t>255261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>737104</t>
+          <t>739759</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>795660</t>
+          <t>792363</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>823930</t>
+          <t>823322</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>878780</t>
+          <t>878928</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1582682</t>
+          <t>1578976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1659258</t>
+          <t>1659034</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175089</t>
+          <t>174306</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239375</t>
+          <t>239426</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188925</t>
+          <t>192710</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>260829</t>
+          <t>260917</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>385425</t>
+          <t>381417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482913</t>
+          <t>484671</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233863</t>
+          <t>235995</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>314410</t>
+          <t>316319</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>219556</t>
+          <t>220515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>280947</t>
+          <t>282692</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>470374</t>
+          <t>476262</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>575599</t>
+          <t>580058</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2746504</t>
+          <t>2749724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2845669</t>
+          <t>2847351</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2853356</t>
+          <t>2858073</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2950493</t>
+          <t>2946200</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5635560</t>
+          <t>5630879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5771939</t>
+          <t>5772031</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2012</t>
+          <t>Población según su lugar de nacimiento en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28557</t>
+          <t>30132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33599</t>
+          <t>31884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60605</t>
+          <t>61191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>43952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82739</t>
+          <t>84007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76309</t>
+          <t>76352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88593</t>
+          <t>93341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145114</t>
+          <t>149668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>592322</t>
+          <t>591906</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>637194</t>
+          <t>635248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>601125</t>
+          <t>600649</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>640512</t>
+          <t>640098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1205928</t>
+          <t>1205457</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1267884</t>
+          <t>1264534</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34752</t>
+          <t>35982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66072</t>
+          <t>67226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>34438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63018</t>
+          <t>62428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76082</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119372</t>
+          <t>120113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108417</t>
+          <t>109326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64763</t>
+          <t>66615</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108845</t>
+          <t>113919</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>133843</t>
+          <t>136765</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>197939</t>
+          <t>203604</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>857648</t>
+          <t>860109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>912149</t>
+          <t>913771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>874199</t>
+          <t>869492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>923905</t>
+          <t>923200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1748548</t>
+          <t>1748010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1824083</t>
+          <t>1823405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59255</t>
+          <t>57573</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94373</t>
+          <t>93062</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77526</t>
+          <t>79053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117378</t>
+          <t>119704</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144876</t>
+          <t>144533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>200592</t>
+          <t>197018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85366</t>
+          <t>85716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138788</t>
+          <t>139219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80490</t>
+          <t>79152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131896</t>
+          <t>129960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176868</t>
+          <t>179537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248786</t>
+          <t>247150</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543200</t>
+          <t>541658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>600862</t>
+          <t>598405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>547733</t>
+          <t>545440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>604322</t>
+          <t>604583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1110872</t>
+          <t>1111458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192832</t>
+          <t>1191378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,62%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44597</t>
+          <t>45133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77315</t>
+          <t>75913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52977</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85146</t>
+          <t>86668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103467</t>
+          <t>104832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152489</t>
+          <t>151432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84236</t>
+          <t>82105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136721</t>
+          <t>137215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83833</t>
+          <t>85805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136286</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181834</t>
+          <t>186634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255046</t>
+          <t>256254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>749957</t>
+          <t>750447</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>807982</t>
+          <t>809455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>844609</t>
+          <t>843527</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>904414</t>
+          <t>903324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1615346</t>
+          <t>1609925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1696929</t>
+          <t>1694527</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179591</t>
+          <t>180123</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239642</t>
+          <t>242768</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>199087</t>
+          <t>202050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264604</t>
+          <t>261790</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>393752</t>
+          <t>400250</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485907</t>
+          <t>484349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>312621</t>
+          <t>314381</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>412346</t>
+          <t>416613</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>306152</t>
+          <t>308447</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>408217</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>641348</t>
+          <t>645546</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>777150</t>
+          <t>786431</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2806691</t>
+          <t>2795138</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2912479</t>
+          <t>2910291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2920951</t>
+          <t>2918346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3030426</t>
+          <t>3027045</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5759187</t>
+          <t>5751375</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5913484</t>
+          <t>5904723</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2016</t>
+          <t>Población según su lugar de nacimiento en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45676</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23485</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46059</t>
+          <t>45791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50062</t>
+          <t>49522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84420</t>
+          <t>81219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40166</t>
+          <t>39855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78360</t>
+          <t>77550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48353</t>
+          <t>47639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85112</t>
+          <t>83581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99042</t>
+          <t>97264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150827</t>
+          <t>149529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>564527</t>
+          <t>562064</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>604623</t>
+          <t>605925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>551090</t>
+          <t>553037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>592265</t>
+          <t>593922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1127479</t>
+          <t>1128793</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1186197</t>
+          <t>1186654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63523</t>
+          <t>62522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102491</t>
+          <t>102240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60719</t>
+          <t>60674</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94250</t>
+          <t>96850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133984</t>
+          <t>135737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184419</t>
+          <t>185632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70087</t>
+          <t>69361</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116178</t>
+          <t>116693</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83298</t>
+          <t>81241</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>134992</t>
+          <t>132140</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,47 +6376,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>195957</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>164990</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>238254</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>7,99%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>195957</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>162370</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>230846</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>822610</t>
+          <t>819991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>878782</t>
+          <t>878033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>830234</t>
+          <t>828379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>888139</t>
+          <t>885085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1672161</t>
+          <t>1667817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1748756</t>
+          <t>1747956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>59583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48296</t>
+          <t>48336</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80482</t>
+          <t>80526</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86708</t>
+          <t>85710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129305</t>
+          <t>130373</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58191</t>
+          <t>57279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97619</t>
+          <t>99900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39765</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77573</t>
+          <t>75588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107093</t>
+          <t>105241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162488</t>
+          <t>163196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614610</t>
+          <t>612947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>661927</t>
+          <t>660177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639542</t>
+          <t>643047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>688014</t>
+          <t>687693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1271798</t>
+          <t>1272796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1336535</t>
+          <t>1339328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70435</t>
+          <t>68629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43926</t>
+          <t>44681</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74818</t>
+          <t>76744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91998</t>
+          <t>92221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134478</t>
+          <t>135439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71559</t>
+          <t>71762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114378</t>
+          <t>115791</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76457</t>
+          <t>77076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125621</t>
+          <t>124659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>158964</t>
+          <t>160314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226306</t>
+          <t>230297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>767785</t>
+          <t>764864</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>816739</t>
+          <t>816446</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>853973</t>
+          <t>855296</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>911156</t>
+          <t>910420</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1639545</t>
+          <t>1637378</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1714950</t>
+          <t>1713241</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178099</t>
+          <t>178617</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239796</t>
+          <t>241047</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>203574</t>
+          <t>202153</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262822</t>
+          <t>259728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>397100</t>
+          <t>400298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>486008</t>
+          <t>482043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>275046</t>
+          <t>274204</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>357798</t>
+          <t>357739</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>284066</t>
+          <t>282727</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>371657</t>
+          <t>372028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>588141</t>
+          <t>581689</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>707018</t>
+          <t>702024</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2821058</t>
+          <t>2821365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2917402</t>
+          <t>2919471</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2934849</t>
+          <t>2934563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3036508</t>
+          <t>3040168</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5784760</t>
+          <t>5789390</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5924398</t>
+          <t>5930353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2023</t>
+          <t>Población según su lugar de nacimiento en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>40942</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15756</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29961</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33502</t>
+          <t>33784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61200</t>
+          <t>62069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>590859</t>
+          <t>589004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>615084</t>
+          <t>613843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>635947</t>
+          <t>637152</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651209</t>
+          <t>651501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1234256</t>
+          <t>1233136</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262873</t>
+          <t>1262685</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,82 +8740,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>14539</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11736</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18110</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>26604</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>22805</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>30933</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14539</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11650</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>17613</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>26604</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>22453</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>31016</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58063</t>
+          <t>57389</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25984</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45524</t>
+          <t>44716</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56781</t>
+          <t>59090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>93419</t>
+          <t>92436</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>869728</t>
+          <t>869778</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>900133</t>
+          <t>900866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>895747</t>
+          <t>896373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>916003</t>
+          <t>916074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1774017</t>
+          <t>1775178</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1812368</t>
+          <t>1809989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26305</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29181</t>
+          <t>29271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38819</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43416</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73017</t>
+          <t>75601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40369</t>
+          <t>38680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61852</t>
+          <t>62226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88816</t>
+          <t>89788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130286</t>
+          <t>128074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>618568</t>
+          <t>617572</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>649763</t>
+          <t>649803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606671</t>
+          <t>608204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>630898</t>
+          <t>632052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1234663</t>
+          <t>1235045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1276616</t>
+          <t>1275349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12959</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21422</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45368</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77721</t>
+          <t>76075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53440</t>
+          <t>52172</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81437</t>
+          <t>80430</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105165</t>
+          <t>105119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149026</t>
+          <t>148433</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>839453</t>
+          <t>840359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>871802</t>
+          <t>873837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>917700</t>
+          <t>917628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>946137</t>
+          <t>946475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1766125</t>
+          <t>1766684</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1811160</t>
+          <t>1810764</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>53601</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66827</t>
+          <t>66061</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92172</t>
+          <t>92570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107747</t>
+          <t>108929</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>151201</t>
+          <t>151383</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>212061</t>
+          <t>211277</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>150494</t>
+          <t>150137</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>192042</t>
+          <t>192495</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>311933</t>
+          <t>315783</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>387820</t>
+          <t>391168</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2954531</t>
+          <t>2954503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3015303</t>
+          <t>3013607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3083494</t>
+          <t>3082487</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3127588</t>
+          <t>3128547</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6055076</t>
+          <t>6048659</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6132702</t>
+          <t>6126963</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P58-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P58-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27112</t>
+          <t>29569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19228</t>
+          <t>18920</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46135</t>
+          <t>46750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30577</t>
+          <t>29607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63731</t>
+          <t>63210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48106</t>
+          <t>49174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45503</t>
+          <t>44549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47305</t>
+          <t>48004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84370</t>
+          <t>83656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>628356</t>
+          <t>626555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>660952</t>
+          <t>661991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>606087</t>
+          <t>608015</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>641411</t>
+          <t>644084</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1246775</t>
+          <t>1244498</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1295852</t>
+          <t>1293715</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38683</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75180</t>
+          <t>75903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>43313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78233</t>
+          <t>78356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87901</t>
+          <t>88978</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138131</t>
+          <t>138854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48955</t>
+          <t>50621</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90528</t>
+          <t>92766</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34640</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63272</t>
+          <t>61553</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92860</t>
+          <t>92245</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>147127</t>
+          <t>143140</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>811497</t>
+          <t>810721</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>863799</t>
+          <t>862788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,82 +1430,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>89,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>863367</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>838809</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>883606</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>89,15%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>86,62%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>91,24%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1701902</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1662684</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1733537</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>88,17%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>86,14%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>89,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>863367</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>838205</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>883894</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>89,15%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>86,56%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1656</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1701902</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1664697</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1735395</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>88,17%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>86,25%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49460</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86351</t>
+          <t>87427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45997</t>
+          <t>48642</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82335</t>
+          <t>81980</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105141</t>
+          <t>104896</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155905</t>
+          <t>158012</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48635</t>
+          <t>47617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88112</t>
+          <t>87925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42975</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73016</t>
+          <t>72768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100714</t>
+          <t>100890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149930</t>
+          <t>149842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>521404</t>
+          <t>519673</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>571543</t>
+          <t>569094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>540794</t>
+          <t>541673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>583191</t>
+          <t>585005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1076143</t>
+          <t>1074164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1141725</t>
+          <t>1140907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50744</t>
+          <t>51888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89344</t>
+          <t>88717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52903</t>
+          <t>54183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95117</t>
+          <t>93774</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116122</t>
+          <t>112875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171235</t>
+          <t>171520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84945</t>
+          <t>82531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131371</t>
+          <t>130219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92561</t>
+          <t>93737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134214</t>
+          <t>135422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188822</t>
+          <t>186715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255261</t>
+          <t>251377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>739759</t>
+          <t>739254</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>792363</t>
+          <t>797246</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>823322</t>
+          <t>825519</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>878928</t>
+          <t>878770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1578976</t>
+          <t>1577875</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1659034</t>
+          <t>1659585</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174306</t>
+          <t>172478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239426</t>
+          <t>242923</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192710</t>
+          <t>192321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>260917</t>
+          <t>264557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>381417</t>
+          <t>381036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>484671</t>
+          <t>478948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>235995</t>
+          <t>235468</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>316319</t>
+          <t>318025</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>220515</t>
+          <t>217477</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>282692</t>
+          <t>280146</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>476262</t>
+          <t>471995</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>580058</t>
+          <t>578127</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2749724</t>
+          <t>2745881</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2847351</t>
+          <t>2848050</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2858073</t>
+          <t>2857046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2946200</t>
+          <t>2948671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5630879</t>
+          <t>5640007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5772031</t>
+          <t>5775166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>17715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39308</t>
+          <t>41293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>29071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,47 +3295,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>45453</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>32679</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>60528</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>4,32%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>45453</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>31884</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>61191</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43952</t>
+          <t>43562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84007</t>
+          <t>84495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39023</t>
+          <t>38904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76352</t>
+          <t>78548</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93341</t>
+          <t>91185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149668</t>
+          <t>145435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>591906</t>
+          <t>590362</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635248</t>
+          <t>634504</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>600649</t>
+          <t>599669</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>640098</t>
+          <t>641764</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1205457</t>
+          <t>1207935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264534</t>
+          <t>1265681</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35982</t>
+          <t>34927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67226</t>
+          <t>64115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34438</t>
+          <t>34207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>64549</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>77072</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120113</t>
+          <t>121397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59485</t>
+          <t>61161</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>109326</t>
+          <t>107287</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66615</t>
+          <t>65300</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>113919</t>
+          <t>113417</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>136765</t>
+          <t>134783</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>203604</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>860109</t>
+          <t>861053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>913771</t>
+          <t>912291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>869492</t>
+          <t>870057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>923200</t>
+          <t>924245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1748010</t>
+          <t>1747009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1823405</t>
+          <t>1825897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57573</t>
+          <t>57210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93062</t>
+          <t>94867</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79053</t>
+          <t>77039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119704</t>
+          <t>116761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144533</t>
+          <t>145914</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197018</t>
+          <t>198680</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85716</t>
+          <t>83383</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139219</t>
+          <t>139051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79152</t>
+          <t>78073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129960</t>
+          <t>128493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179537</t>
+          <t>178030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247150</t>
+          <t>252663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>541658</t>
+          <t>544819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>598405</t>
+          <t>603760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>545440</t>
+          <t>548679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>604583</t>
+          <t>604346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1111458</t>
+          <t>1109978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1191378</t>
+          <t>1190028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45133</t>
+          <t>43686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75913</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53897</t>
+          <t>51937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86668</t>
+          <t>86953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104832</t>
+          <t>106317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151432</t>
+          <t>153976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -4726,49 +4726,49 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82105</t>
+          <t>82414</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>136638</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>110176</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>86370</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>137215</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>110176</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>85805</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>136520</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,47%</t>
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186634</t>
+          <t>183201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>256254</t>
+          <t>255378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>750447</t>
+          <t>751719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>809455</t>
+          <t>810407</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>843527</t>
+          <t>843725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>903324</t>
+          <t>902017</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1609925</t>
+          <t>1611276</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1694527</t>
+          <t>1693070</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180123</t>
+          <t>180293</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242768</t>
+          <t>238616</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>202050</t>
+          <t>203211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261790</t>
+          <t>268587</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400250</t>
+          <t>398292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>484349</t>
+          <t>486521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>314381</t>
+          <t>309837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>416613</t>
+          <t>411428</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>308447</t>
+          <t>307810</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>408217</t>
+          <t>401156</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>645546</t>
+          <t>643726</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>786431</t>
+          <t>777752</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2795138</t>
+          <t>2803532</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2910291</t>
+          <t>2911479</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2918346</t>
+          <t>2917725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3027045</t>
+          <t>3027214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5751375</t>
+          <t>5759053</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5904723</t>
+          <t>5911883</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>21818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>46327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45791</t>
+          <t>45755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49522</t>
+          <t>49208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>81486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39855</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77550</t>
+          <t>79808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47639</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83581</t>
+          <t>85587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97264</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149529</t>
+          <t>151453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>562064</t>
+          <t>563424</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>605925</t>
+          <t>605455</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>553037</t>
+          <t>551131</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>593922</t>
+          <t>592891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1128793</t>
+          <t>1132440</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1186654</t>
+          <t>1188815</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62522</t>
+          <t>63650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102240</t>
+          <t>103261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60674</t>
+          <t>60857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96850</t>
+          <t>95485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135737</t>
+          <t>130334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>185632</t>
+          <t>184812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69361</t>
+          <t>68182</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116693</t>
+          <t>113785</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81241</t>
+          <t>84465</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>132140</t>
+          <t>134503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>164990</t>
+          <t>165535</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>238254</t>
+          <t>230758</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>819991</t>
+          <t>820935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>878033</t>
+          <t>876738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>828379</t>
+          <t>831871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>885085</t>
+          <t>884817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1667817</t>
+          <t>1669504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1747956</t>
+          <t>1749539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,71%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30882</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>60182</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48336</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80526</t>
+          <t>78390</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85710</t>
+          <t>86255</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>130373</t>
+          <t>127908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57279</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99900</t>
+          <t>97253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>39196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75588</t>
+          <t>76201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105241</t>
+          <t>104472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163196</t>
+          <t>160714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612947</t>
+          <t>612507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>660177</t>
+          <t>662888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>643047</t>
+          <t>640650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>687693</t>
+          <t>689359</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1272796</t>
+          <t>1275039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1339328</t>
+          <t>1339508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68629</t>
+          <t>71430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76744</t>
+          <t>74167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92221</t>
+          <t>92572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135439</t>
+          <t>134346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71762</t>
+          <t>73490</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115791</t>
+          <t>117248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77076</t>
+          <t>75339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124659</t>
+          <t>124663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>160314</t>
+          <t>159405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230297</t>
+          <t>224364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>764864</t>
+          <t>766254</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>816446</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>855296</t>
+          <t>857160</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>910420</t>
+          <t>911313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1637378</t>
+          <t>1640415</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1713241</t>
+          <t>1714409</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178617</t>
+          <t>180086</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241047</t>
+          <t>240430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>202153</t>
+          <t>203796</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259728</t>
+          <t>263276</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400298</t>
+          <t>400647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482043</t>
+          <t>485099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>274204</t>
+          <t>276436</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>357739</t>
+          <t>356515</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>282727</t>
+          <t>284269</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>372028</t>
+          <t>373978</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>581689</t>
+          <t>588620</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>702024</t>
+          <t>706338</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2821365</t>
+          <t>2820761</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2919471</t>
+          <t>2919993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2934563</t>
+          <t>2934752</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3040168</t>
+          <t>3036402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5789390</t>
+          <t>5789742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5930353</t>
+          <t>5925147</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>30501</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>58387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>34639</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>25460</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>45770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14561</t>
+          <t>77427</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>62025</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>96055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40942</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29583</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>45446</t>
+          <t>45983</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>34830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62069</t>
+          <t>62200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>605232</t>
+          <t>624092</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>589004</t>
+          <t>602610</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>613843</t>
+          <t>639314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>645241</t>
+          <t>675600</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>637152</t>
+          <t>662725</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651501</t>
+          <t>685747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1250474</t>
+          <t>1299693</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1233136</t>
+          <t>1276277</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262685</t>
+          <t>1319242</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>675040</t>
+          <t>732392</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675040</t>
+          <t>732392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>675040</t>
+          <t>732392</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1310481</t>
+          <t>1423102</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1310481</t>
+          <t>1423102</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1310481</t>
+          <t>1423102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>91029</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>72606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>113425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>68212</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>54794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18110</t>
+          <t>85731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>159241</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>134404</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30933</t>
+          <t>187009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39676</t>
+          <t>39528</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>27092</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57389</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,67 +8868,67 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>35476</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44716</t>
+          <t>47280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>75004</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>60461</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>94890</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>3,54%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>73526</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>59090</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>92436</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>887481</t>
+          <t>916038</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>869778</t>
+          <t>890269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>900866</t>
+          <t>939229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>907271</t>
+          <t>965868</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>896373</t>
+          <t>945111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>916074</t>
+          <t>981017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1794752</t>
+          <t>1881905</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1775178</t>
+          <t>1851637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1809989</t>
+          <t>1911211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>939223</t>
+          <t>1046594</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>939223</t>
+          <t>1046594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>939223</t>
+          <t>1046594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>955659</t>
+          <t>1069556</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>955659</t>
+          <t>1069556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>955659</t>
+          <t>1069556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1894882</t>
+          <t>2116150</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1894882</t>
+          <t>2116150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1894882</t>
+          <t>2116150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>92161</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>73610</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>117307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>114811</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>96258</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>135078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>206972</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29271</t>
+          <t>179999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39023</t>
+          <t>235142</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57486</t>
+          <t>58710</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43957</t>
+          <t>44169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75601</t>
+          <t>76792</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>51334</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>39705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62226</t>
+          <t>64133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>106795</t>
+          <t>110044</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89788</t>
+          <t>91836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128074</t>
+          <t>132314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>635476</t>
+          <t>652202</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>617572</t>
+          <t>625199</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>649803</t>
+          <t>675425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>620845</t>
+          <t>641847</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608204</t>
+          <t>620282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>632052</t>
+          <t>663368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1256322</t>
+          <t>1294049</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1235045</t>
+          <t>1261553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1275349</t>
+          <t>1326530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>692434</t>
+          <t>807992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>692434</t>
+          <t>807992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>692434</t>
+          <t>807992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1397115</t>
+          <t>1611065</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1397115</t>
+          <t>1611065</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1397115</t>
+          <t>1611065</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>72167</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>55421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12799</t>
+          <t>95017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>77250</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>63212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>96511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>149417</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>127012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29181</t>
+          <t>175444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>58642</t>
+          <t>58553</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42811</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76075</t>
+          <t>75186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>65209</t>
+          <t>66800</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52172</t>
+          <t>53462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80430</t>
+          <t>82527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>123851</t>
+          <t>125353</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105119</t>
+          <t>108072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148433</t>
+          <t>150358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>858080</t>
+          <t>859342</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>840359</t>
+          <t>833741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>873837</t>
+          <t>879755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933334</t>
+          <t>970944</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>917628</t>
+          <t>948007</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>946475</t>
+          <t>991040</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1791414</t>
+          <t>1830286</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1766684</t>
+          <t>1797060</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1810764</t>
+          <t>1858850</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1013657</t>
+          <t>1114994</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1013657</t>
+          <t>1114994</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1013657</t>
+          <t>1114994</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1940488</t>
+          <t>2105056</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1940488</t>
+          <t>2105056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1940488</t>
+          <t>2105056</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>40502</t>
+          <t>298144</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>261074</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>337464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>59884</t>
+          <t>294912</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53601</t>
+          <t>265536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66061</t>
+          <t>328000</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>100386</t>
+          <t>593056</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92570</t>
+          <t>543058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108929</t>
+          <t>646321</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -10201,67 +10201,67 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>179403</t>
+          <t>180621</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>151383</t>
+          <t>154093</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>211277</t>
+          <t>210329</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>175763</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>155269</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>201250</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>170215</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>192495</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>349618</t>
+          <t>356384</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>315783</t>
+          <t>319941</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>391168</t>
+          <t>395752</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2986271</t>
+          <t>3051674</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2954503</t>
+          <t>3003363</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3013607</t>
+          <t>3095472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3106690</t>
+          <t>3254260</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3082487</t>
+          <t>3215621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3128547</t>
+          <t>3292061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6092961</t>
+          <t>6305933</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6048659</t>
+          <t>6240182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6126963</t>
+          <t>6365423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3206176</t>
+          <t>3530439</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3206176</t>
+          <t>3530439</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3206176</t>
+          <t>3530439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3336790</t>
+          <t>3724935</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3336790</t>
+          <t>3724935</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3336790</t>
+          <t>3724935</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6542966</t>
+          <t>7255373</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6542966</t>
+          <t>7255373</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6542966</t>
+          <t>7255373</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
